--- a/public/template_solicitud.xlsx
+++ b/public/template_solicitud.xlsx
@@ -1,19 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://avantikacolombia-my.sharepoint.com/personal/sistemas_avantika_com_co/Documents/Documentos/DesarrollosWeb/AvantikaSolicitudACompras/Frontend/solicitudes/public/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vnieto\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="13_ncr:1_{F4F170ED-8859-4489-B77A-844553947681}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{27730F59-449C-4274-A8FE-E7F57ADE57D5}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0345E480-C8AA-430B-A1DE-8E3614E53BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{AACE1D6A-3F3A-F04E-81B1-EF08C7442AA3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AACE1D6A-3F3A-F04E-81B1-EF08C7442AA3}"/>
   </bookViews>
   <sheets>
     <sheet name="Hoja1" sheetId="1" r:id="rId1"/>
+    <sheet name="negociadores" sheetId="2" r:id="rId2"/>
   </sheets>
   <calcPr calcId="181029"/>
   <extLst>
@@ -36,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5" uniqueCount="5">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
   <si>
     <t>referencia</t>
   </si>
@@ -51,6 +52,33 @@
   </si>
   <si>
     <t>marca</t>
+  </si>
+  <si>
+    <t>negociador</t>
+  </si>
+  <si>
+    <t>usuario</t>
+  </si>
+  <si>
+    <t>nombre</t>
+  </si>
+  <si>
+    <t>MMIRANDA2</t>
+  </si>
+  <si>
+    <t>NFERNANDEZ</t>
+  </si>
+  <si>
+    <t>PCARBONELL</t>
+  </si>
+  <si>
+    <t>Mileinis Miranda</t>
+  </si>
+  <si>
+    <t>Nicol Fernandez</t>
+  </si>
+  <si>
+    <t>Paola Carbonell</t>
   </si>
 </sst>
 </file>
@@ -87,7 +115,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -110,11 +138,22 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center"/>
@@ -132,6 +171,11 @@
     <xf numFmtId="1" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyProtection="1">
       <protection locked="0"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -147,6 +191,17 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FE82A2A1-8FD2-409E-B715-FAE4870AFD0F}" name="Tabla2" displayName="Tabla2" ref="A1:B4" totalsRowShown="0">
+  <autoFilter ref="A1:B4" xr:uid="{FE82A2A1-8FD2-409E-B715-FAE4870AFD0F}"/>
+  <tableColumns count="2">
+    <tableColumn id="1" xr3:uid="{906D9EC4-93F1-46F6-B1EF-540BF3388EBF}" name="usuario"/>
+    <tableColumn id="2" xr3:uid="{2DCD90C0-441C-4703-BDA3-36E1DC163D1E}" name="nombre"/>
+  </tableColumns>
+  <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+</table>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -466,15 +521,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A1D47E0E-B32A-DC4A-87B8-B8F08D05D8EB}">
-  <dimension ref="A1:E100"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.4"/>
+  <dimension ref="A1:F100"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="10.6640625" style="2"/>
-    <col min="3" max="3" width="10.6640625" style="5"/>
-    <col min="4" max="5" width="10.6640625" style="2"/>
+    <col min="1" max="1" width="13" style="2" customWidth="1"/>
+    <col min="2" max="2" width="15" style="2" customWidth="1"/>
+    <col min="3" max="3" width="13" style="5" customWidth="1"/>
+    <col min="4" max="5" width="10.69921875" style="2"/>
+    <col min="6" max="6" width="15.8984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="19" customHeight="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:6" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -490,702 +547,803 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F1" s="6" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" s="3"/>
       <c r="B2" s="3"/>
       <c r="C2" s="4"/>
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
-    </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F2" s="7"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" s="3"/>
       <c r="B3" s="3"/>
       <c r="C3" s="4"/>
       <c r="D3" s="3"/>
       <c r="E3" s="3"/>
-    </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F3" s="7"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4" s="3"/>
       <c r="B4" s="3"/>
       <c r="C4" s="4"/>
       <c r="D4" s="3"/>
       <c r="E4" s="3"/>
-    </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F4" s="7"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5" s="3"/>
       <c r="B5" s="3"/>
       <c r="C5" s="4"/>
       <c r="D5" s="3"/>
       <c r="E5" s="3"/>
-    </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F5" s="7"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6" s="3"/>
       <c r="B6" s="3"/>
       <c r="C6" s="4"/>
       <c r="D6" s="3"/>
       <c r="E6" s="3"/>
-    </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F6" s="7"/>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7" s="3"/>
       <c r="B7" s="3"/>
       <c r="C7" s="4"/>
       <c r="D7" s="3"/>
       <c r="E7" s="3"/>
-    </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F7" s="7"/>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
       <c r="B8" s="3"/>
       <c r="C8" s="4"/>
       <c r="D8" s="3"/>
       <c r="E8" s="3"/>
-    </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F8" s="7"/>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
       <c r="B9" s="3"/>
       <c r="C9" s="4"/>
       <c r="D9" s="3"/>
       <c r="E9" s="3"/>
-    </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F9" s="7"/>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10" s="3"/>
       <c r="B10" s="3"/>
       <c r="C10" s="4"/>
       <c r="D10" s="3"/>
       <c r="E10" s="3"/>
-    </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F10" s="7"/>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11" s="3"/>
       <c r="B11" s="3"/>
       <c r="C11" s="4"/>
       <c r="D11" s="3"/>
       <c r="E11" s="3"/>
-    </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F11" s="7"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="3"/>
       <c r="B12" s="3"/>
       <c r="C12" s="4"/>
       <c r="D12" s="3"/>
       <c r="E12" s="3"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F12" s="7"/>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A13" s="3"/>
       <c r="B13" s="3"/>
       <c r="C13" s="4"/>
       <c r="D13" s="3"/>
       <c r="E13" s="3"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F13" s="7"/>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A14" s="3"/>
       <c r="B14" s="3"/>
       <c r="C14" s="4"/>
       <c r="D14" s="3"/>
       <c r="E14" s="3"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F14" s="7"/>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A15" s="3"/>
       <c r="B15" s="3"/>
       <c r="C15" s="4"/>
       <c r="D15" s="3"/>
       <c r="E15" s="3"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F15" s="7"/>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A16" s="3"/>
       <c r="B16" s="3"/>
       <c r="C16" s="4"/>
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
-    </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F16" s="7"/>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A17" s="3"/>
       <c r="B17" s="3"/>
       <c r="C17" s="4"/>
       <c r="D17" s="3"/>
       <c r="E17" s="3"/>
-    </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F17" s="7"/>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A18" s="3"/>
       <c r="B18" s="3"/>
       <c r="C18" s="4"/>
       <c r="D18" s="3"/>
       <c r="E18" s="3"/>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F18" s="7"/>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A19" s="3"/>
       <c r="B19" s="3"/>
       <c r="C19" s="4"/>
       <c r="D19" s="3"/>
       <c r="E19" s="3"/>
-    </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F19" s="7"/>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A20" s="3"/>
       <c r="B20" s="3"/>
       <c r="C20" s="4"/>
       <c r="D20" s="3"/>
       <c r="E20" s="3"/>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F20" s="7"/>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A21" s="3"/>
       <c r="B21" s="3"/>
       <c r="C21" s="4"/>
       <c r="D21" s="3"/>
       <c r="E21" s="3"/>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F21" s="7"/>
+    </row>
+    <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="3"/>
       <c r="B22" s="3"/>
       <c r="C22" s="4"/>
       <c r="D22" s="3"/>
       <c r="E22" s="3"/>
-    </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F22" s="7"/>
+    </row>
+    <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="3"/>
       <c r="B23" s="3"/>
       <c r="C23" s="4"/>
       <c r="D23" s="3"/>
       <c r="E23" s="3"/>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F23" s="7"/>
+    </row>
+    <row r="24" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A24" s="3"/>
       <c r="B24" s="3"/>
       <c r="C24" s="4"/>
       <c r="D24" s="3"/>
       <c r="E24" s="3"/>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F24" s="7"/>
+    </row>
+    <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="3"/>
       <c r="B25" s="3"/>
       <c r="C25" s="4"/>
       <c r="D25" s="3"/>
       <c r="E25" s="3"/>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F25" s="7"/>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="3"/>
       <c r="B26" s="3"/>
       <c r="C26" s="4"/>
       <c r="D26" s="3"/>
       <c r="E26" s="3"/>
-    </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F26" s="7"/>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="3"/>
       <c r="B27" s="3"/>
       <c r="C27" s="4"/>
       <c r="D27" s="3"/>
       <c r="E27" s="3"/>
-    </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F27" s="7"/>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="3"/>
       <c r="B28" s="3"/>
       <c r="C28" s="4"/>
       <c r="D28" s="3"/>
       <c r="E28" s="3"/>
-    </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F28" s="7"/>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A29" s="3"/>
       <c r="B29" s="3"/>
       <c r="C29" s="4"/>
       <c r="D29" s="3"/>
       <c r="E29" s="3"/>
-    </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F29" s="7"/>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A30" s="3"/>
       <c r="B30" s="3"/>
       <c r="C30" s="4"/>
       <c r="D30" s="3"/>
       <c r="E30" s="3"/>
-    </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F30" s="7"/>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A31" s="3"/>
       <c r="B31" s="3"/>
       <c r="C31" s="4"/>
       <c r="D31" s="3"/>
       <c r="E31" s="3"/>
-    </row>
-    <row r="32" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F31" s="7"/>
+    </row>
+    <row r="32" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A32" s="3"/>
       <c r="B32" s="3"/>
       <c r="C32" s="4"/>
       <c r="D32" s="3"/>
       <c r="E32" s="3"/>
-    </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F32" s="7"/>
+    </row>
+    <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="3"/>
       <c r="B33" s="3"/>
       <c r="C33" s="4"/>
       <c r="D33" s="3"/>
       <c r="E33" s="3"/>
-    </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F33" s="7"/>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A34" s="3"/>
       <c r="B34" s="3"/>
       <c r="C34" s="4"/>
       <c r="D34" s="3"/>
       <c r="E34" s="3"/>
-    </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F34" s="7"/>
+    </row>
+    <row r="35" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A35" s="3"/>
       <c r="B35" s="3"/>
       <c r="C35" s="4"/>
       <c r="D35" s="3"/>
       <c r="E35" s="3"/>
-    </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F35" s="7"/>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A36" s="3"/>
       <c r="B36" s="3"/>
       <c r="C36" s="4"/>
       <c r="D36" s="3"/>
       <c r="E36" s="3"/>
-    </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F36" s="7"/>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="3"/>
       <c r="B37" s="3"/>
       <c r="C37" s="4"/>
       <c r="D37" s="3"/>
       <c r="E37" s="3"/>
-    </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F37" s="7"/>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="3"/>
       <c r="B38" s="3"/>
       <c r="C38" s="4"/>
       <c r="D38" s="3"/>
       <c r="E38" s="3"/>
-    </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F38" s="7"/>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="3"/>
       <c r="B39" s="3"/>
       <c r="C39" s="4"/>
       <c r="D39" s="3"/>
       <c r="E39" s="3"/>
-    </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F39" s="7"/>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A40" s="3"/>
       <c r="B40" s="3"/>
       <c r="C40" s="4"/>
       <c r="D40" s="3"/>
       <c r="E40" s="3"/>
-    </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F40" s="7"/>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A41" s="3"/>
       <c r="B41" s="3"/>
       <c r="C41" s="4"/>
       <c r="D41" s="3"/>
       <c r="E41" s="3"/>
-    </row>
-    <row r="42" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F41" s="7"/>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A42" s="3"/>
       <c r="B42" s="3"/>
       <c r="C42" s="4"/>
       <c r="D42" s="3"/>
       <c r="E42" s="3"/>
-    </row>
-    <row r="43" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F42" s="7"/>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A43" s="3"/>
       <c r="B43" s="3"/>
       <c r="C43" s="4"/>
       <c r="D43" s="3"/>
       <c r="E43" s="3"/>
-    </row>
-    <row r="44" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F43" s="7"/>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A44" s="3"/>
       <c r="B44" s="3"/>
       <c r="C44" s="4"/>
       <c r="D44" s="3"/>
       <c r="E44" s="3"/>
-    </row>
-    <row r="45" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F44" s="7"/>
+    </row>
+    <row r="45" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A45" s="3"/>
       <c r="B45" s="3"/>
       <c r="C45" s="4"/>
       <c r="D45" s="3"/>
       <c r="E45" s="3"/>
-    </row>
-    <row r="46" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F45" s="7"/>
+    </row>
+    <row r="46" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A46" s="3"/>
       <c r="B46" s="3"/>
       <c r="C46" s="4"/>
       <c r="D46" s="3"/>
       <c r="E46" s="3"/>
-    </row>
-    <row r="47" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F46" s="7"/>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A47" s="3"/>
       <c r="B47" s="3"/>
       <c r="C47" s="4"/>
       <c r="D47" s="3"/>
       <c r="E47" s="3"/>
-    </row>
-    <row r="48" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F47" s="7"/>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A48" s="3"/>
       <c r="B48" s="3"/>
       <c r="C48" s="4"/>
       <c r="D48" s="3"/>
       <c r="E48" s="3"/>
-    </row>
-    <row r="49" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F48" s="7"/>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A49" s="3"/>
       <c r="B49" s="3"/>
       <c r="C49" s="4"/>
       <c r="D49" s="3"/>
       <c r="E49" s="3"/>
-    </row>
-    <row r="50" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F49" s="7"/>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A50" s="3"/>
       <c r="B50" s="3"/>
       <c r="C50" s="4"/>
       <c r="D50" s="3"/>
       <c r="E50" s="3"/>
-    </row>
-    <row r="51" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F50" s="7"/>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A51" s="3"/>
       <c r="B51" s="3"/>
       <c r="C51" s="4"/>
       <c r="D51" s="3"/>
       <c r="E51" s="3"/>
-    </row>
-    <row r="52" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F51" s="7"/>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A52" s="3"/>
       <c r="B52" s="3"/>
       <c r="C52" s="4"/>
       <c r="D52" s="3"/>
       <c r="E52" s="3"/>
-    </row>
-    <row r="53" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F52" s="7"/>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A53" s="3"/>
       <c r="B53" s="3"/>
       <c r="C53" s="4"/>
       <c r="D53" s="3"/>
       <c r="E53" s="3"/>
-    </row>
-    <row r="54" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F53" s="7"/>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A54" s="3"/>
       <c r="B54" s="3"/>
       <c r="C54" s="4"/>
       <c r="D54" s="3"/>
       <c r="E54" s="3"/>
-    </row>
-    <row r="55" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F54" s="7"/>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A55" s="3"/>
       <c r="B55" s="3"/>
       <c r="C55" s="4"/>
       <c r="D55" s="3"/>
       <c r="E55" s="3"/>
-    </row>
-    <row r="56" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F55" s="7"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="3"/>
       <c r="B56" s="3"/>
       <c r="C56" s="4"/>
       <c r="D56" s="3"/>
       <c r="E56" s="3"/>
-    </row>
-    <row r="57" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F56" s="7"/>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A57" s="3"/>
       <c r="B57" s="3"/>
       <c r="C57" s="4"/>
       <c r="D57" s="3"/>
       <c r="E57" s="3"/>
-    </row>
-    <row r="58" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F57" s="7"/>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="3"/>
       <c r="B58" s="3"/>
       <c r="C58" s="4"/>
       <c r="D58" s="3"/>
       <c r="E58" s="3"/>
-    </row>
-    <row r="59" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F58" s="7"/>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A59" s="3"/>
       <c r="B59" s="3"/>
       <c r="C59" s="4"/>
       <c r="D59" s="3"/>
       <c r="E59" s="3"/>
-    </row>
-    <row r="60" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F59" s="7"/>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A60" s="3"/>
       <c r="B60" s="3"/>
       <c r="C60" s="4"/>
       <c r="D60" s="3"/>
       <c r="E60" s="3"/>
-    </row>
-    <row r="61" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F60" s="7"/>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A61" s="3"/>
       <c r="B61" s="3"/>
       <c r="C61" s="4"/>
       <c r="D61" s="3"/>
       <c r="E61" s="3"/>
-    </row>
-    <row r="62" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F61" s="7"/>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A62" s="3"/>
       <c r="B62" s="3"/>
       <c r="C62" s="4"/>
       <c r="D62" s="3"/>
       <c r="E62" s="3"/>
-    </row>
-    <row r="63" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F62" s="7"/>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A63" s="3"/>
       <c r="B63" s="3"/>
       <c r="C63" s="4"/>
       <c r="D63" s="3"/>
       <c r="E63" s="3"/>
-    </row>
-    <row r="64" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F63" s="7"/>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A64" s="3"/>
       <c r="B64" s="3"/>
       <c r="C64" s="4"/>
       <c r="D64" s="3"/>
       <c r="E64" s="3"/>
-    </row>
-    <row r="65" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F64" s="7"/>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A65" s="3"/>
       <c r="B65" s="3"/>
       <c r="C65" s="4"/>
       <c r="D65" s="3"/>
       <c r="E65" s="3"/>
-    </row>
-    <row r="66" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F65" s="7"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A66" s="3"/>
       <c r="B66" s="3"/>
       <c r="C66" s="4"/>
       <c r="D66" s="3"/>
       <c r="E66" s="3"/>
-    </row>
-    <row r="67" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F66" s="7"/>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A67" s="3"/>
       <c r="B67" s="3"/>
       <c r="C67" s="4"/>
       <c r="D67" s="3"/>
       <c r="E67" s="3"/>
-    </row>
-    <row r="68" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F67" s="7"/>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A68" s="3"/>
       <c r="B68" s="3"/>
       <c r="C68" s="4"/>
       <c r="D68" s="3"/>
       <c r="E68" s="3"/>
-    </row>
-    <row r="69" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F68" s="7"/>
+    </row>
+    <row r="69" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A69" s="3"/>
       <c r="B69" s="3"/>
       <c r="C69" s="4"/>
       <c r="D69" s="3"/>
       <c r="E69" s="3"/>
-    </row>
-    <row r="70" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F69" s="7"/>
+    </row>
+    <row r="70" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A70" s="3"/>
       <c r="B70" s="3"/>
       <c r="C70" s="4"/>
       <c r="D70" s="3"/>
       <c r="E70" s="3"/>
-    </row>
-    <row r="71" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F70" s="7"/>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A71" s="3"/>
       <c r="B71" s="3"/>
       <c r="C71" s="4"/>
       <c r="D71" s="3"/>
       <c r="E71" s="3"/>
-    </row>
-    <row r="72" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F71" s="7"/>
+    </row>
+    <row r="72" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A72" s="3"/>
       <c r="B72" s="3"/>
       <c r="C72" s="4"/>
       <c r="D72" s="3"/>
       <c r="E72" s="3"/>
-    </row>
-    <row r="73" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F72" s="7"/>
+    </row>
+    <row r="73" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A73" s="3"/>
       <c r="B73" s="3"/>
       <c r="C73" s="4"/>
       <c r="D73" s="3"/>
       <c r="E73" s="3"/>
-    </row>
-    <row r="74" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F73" s="7"/>
+    </row>
+    <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="3"/>
       <c r="B74" s="3"/>
       <c r="C74" s="4"/>
       <c r="D74" s="3"/>
       <c r="E74" s="3"/>
-    </row>
-    <row r="75" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F74" s="7"/>
+    </row>
+    <row r="75" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A75" s="3"/>
       <c r="B75" s="3"/>
       <c r="C75" s="4"/>
       <c r="D75" s="3"/>
       <c r="E75" s="3"/>
-    </row>
-    <row r="76" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F75" s="7"/>
+    </row>
+    <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="3"/>
       <c r="B76" s="3"/>
       <c r="C76" s="4"/>
       <c r="D76" s="3"/>
       <c r="E76" s="3"/>
-    </row>
-    <row r="77" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F76" s="7"/>
+    </row>
+    <row r="77" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A77" s="3"/>
       <c r="B77" s="3"/>
       <c r="C77" s="4"/>
       <c r="D77" s="3"/>
       <c r="E77" s="3"/>
-    </row>
-    <row r="78" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F77" s="7"/>
+    </row>
+    <row r="78" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A78" s="3"/>
       <c r="B78" s="3"/>
       <c r="C78" s="4"/>
       <c r="D78" s="3"/>
       <c r="E78" s="3"/>
-    </row>
-    <row r="79" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F78" s="7"/>
+    </row>
+    <row r="79" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A79" s="3"/>
       <c r="B79" s="3"/>
       <c r="C79" s="4"/>
       <c r="D79" s="3"/>
       <c r="E79" s="3"/>
-    </row>
-    <row r="80" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F79" s="7"/>
+    </row>
+    <row r="80" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A80" s="3"/>
       <c r="B80" s="3"/>
       <c r="C80" s="4"/>
       <c r="D80" s="3"/>
       <c r="E80" s="3"/>
-    </row>
-    <row r="81" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F80" s="7"/>
+    </row>
+    <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="3"/>
       <c r="B81" s="3"/>
       <c r="C81" s="4"/>
       <c r="D81" s="3"/>
       <c r="E81" s="3"/>
-    </row>
-    <row r="82" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F81" s="7"/>
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="3"/>
       <c r="B82" s="3"/>
       <c r="C82" s="4"/>
       <c r="D82" s="3"/>
       <c r="E82" s="3"/>
-    </row>
-    <row r="83" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F82" s="7"/>
+    </row>
+    <row r="83" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A83" s="3"/>
       <c r="B83" s="3"/>
       <c r="C83" s="4"/>
       <c r="D83" s="3"/>
       <c r="E83" s="3"/>
-    </row>
-    <row r="84" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F83" s="7"/>
+    </row>
+    <row r="84" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A84" s="3"/>
       <c r="B84" s="3"/>
       <c r="C84" s="4"/>
       <c r="D84" s="3"/>
       <c r="E84" s="3"/>
-    </row>
-    <row r="85" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F84" s="7"/>
+    </row>
+    <row r="85" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A85" s="3"/>
       <c r="B85" s="3"/>
       <c r="C85" s="4"/>
       <c r="D85" s="3"/>
       <c r="E85" s="3"/>
-    </row>
-    <row r="86" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F85" s="7"/>
+    </row>
+    <row r="86" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A86" s="3"/>
       <c r="B86" s="3"/>
       <c r="C86" s="4"/>
       <c r="D86" s="3"/>
       <c r="E86" s="3"/>
-    </row>
-    <row r="87" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F86" s="7"/>
+    </row>
+    <row r="87" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A87" s="3"/>
       <c r="B87" s="3"/>
       <c r="C87" s="4"/>
       <c r="D87" s="3"/>
       <c r="E87" s="3"/>
-    </row>
-    <row r="88" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F87" s="7"/>
+    </row>
+    <row r="88" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A88" s="3"/>
       <c r="B88" s="3"/>
       <c r="C88" s="4"/>
       <c r="D88" s="3"/>
       <c r="E88" s="3"/>
-    </row>
-    <row r="89" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F88" s="7"/>
+    </row>
+    <row r="89" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A89" s="3"/>
       <c r="B89" s="3"/>
       <c r="C89" s="4"/>
       <c r="D89" s="3"/>
       <c r="E89" s="3"/>
-    </row>
-    <row r="90" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F89" s="7"/>
+    </row>
+    <row r="90" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A90" s="3"/>
       <c r="B90" s="3"/>
       <c r="C90" s="4"/>
       <c r="D90" s="3"/>
       <c r="E90" s="3"/>
-    </row>
-    <row r="91" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F90" s="7"/>
+    </row>
+    <row r="91" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A91" s="3"/>
       <c r="B91" s="3"/>
       <c r="C91" s="4"/>
       <c r="D91" s="3"/>
       <c r="E91" s="3"/>
-    </row>
-    <row r="92" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F91" s="7"/>
+    </row>
+    <row r="92" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A92" s="3"/>
       <c r="B92" s="3"/>
       <c r="C92" s="4"/>
       <c r="D92" s="3"/>
       <c r="E92" s="3"/>
-    </row>
-    <row r="93" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F92" s="7"/>
+    </row>
+    <row r="93" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A93" s="3"/>
       <c r="B93" s="3"/>
       <c r="C93" s="4"/>
       <c r="D93" s="3"/>
       <c r="E93" s="3"/>
-    </row>
-    <row r="94" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F93" s="7"/>
+    </row>
+    <row r="94" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A94" s="3"/>
       <c r="B94" s="3"/>
       <c r="C94" s="4"/>
       <c r="D94" s="3"/>
       <c r="E94" s="3"/>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F94" s="7"/>
+    </row>
+    <row r="95" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A95" s="3"/>
       <c r="B95" s="3"/>
       <c r="C95" s="4"/>
       <c r="D95" s="3"/>
       <c r="E95" s="3"/>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F95" s="7"/>
+    </row>
+    <row r="96" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A96" s="3"/>
       <c r="B96" s="3"/>
       <c r="C96" s="4"/>
       <c r="D96" s="3"/>
       <c r="E96" s="3"/>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F96" s="7"/>
+    </row>
+    <row r="97" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A97" s="3"/>
       <c r="B97" s="3"/>
       <c r="C97" s="4"/>
       <c r="D97" s="3"/>
       <c r="E97" s="3"/>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F97" s="7"/>
+    </row>
+    <row r="98" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A98" s="3"/>
       <c r="B98" s="3"/>
       <c r="C98" s="4"/>
       <c r="D98" s="3"/>
       <c r="E98" s="3"/>
-    </row>
-    <row r="99" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F98" s="7"/>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A99" s="3"/>
       <c r="B99" s="3"/>
       <c r="C99" s="4"/>
       <c r="D99" s="3"/>
       <c r="E99" s="3"/>
-    </row>
-    <row r="100" spans="1:5" x14ac:dyDescent="0.4">
+      <c r="F99" s="7"/>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A100" s="3"/>
       <c r="B100" s="3"/>
       <c r="C100" s="4"/>
       <c r="D100" s="3"/>
       <c r="E100" s="3"/>
+      <c r="F100" s="7"/>
     </row>
   </sheetData>
-  <sheetProtection algorithmName="SHA-512" hashValue="ZKmvwMXwZdXXc64uVh93inOMQdoMVaJm9U0ZBUCf8RvoS2yqJfwKH38cuCxrCscrneVuunhJT5vJcEYPQqsdAQ==" saltValue="01dG4+Pw1lug8yfFgOMm4Q==" spinCount="100000" sheet="1" objects="1" scenarios="1"/>
   <dataValidations count="2">
     <dataValidation type="whole" operator="greaterThan" allowBlank="1" showInputMessage="1" showErrorMessage="1" errorTitle="Error Validación" error="Solo se aceptan valores numéricos." sqref="C2:C1048560" xr:uid="{21307D74-6870-4079-9DD6-E62D54811AD7}">
       <formula1>0</formula1>
@@ -1197,4 +1355,53 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DEAF6A5-933D-4C2D-A63D-6B3D9DD19763}">
+  <dimension ref="A1:B4"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="16.3984375" customWidth="1"/>
+    <col min="2" max="2" width="30.5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B1" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>8</v>
+      </c>
+      <c r="B2" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <tableParts count="1">
+    <tablePart r:id="rId1"/>
+  </tableParts>
+</worksheet>
 </file>
--- a/public/template_solicitud.xlsx
+++ b/public/template_solicitud.xlsx
@@ -5,10 +5,10 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vnieto\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\vnieto\Downloads\DesarrollosWeb\AvantikaSolicitudACompras\frontend_solicitudes_a_compras\public\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0345E480-C8AA-430B-A1DE-8E3614E53BE7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4B475511-6928-4823-A718-1D15B8A03F6D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{AACE1D6A-3F3A-F04E-81B1-EF08C7442AA3}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="14" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="10" uniqueCount="10">
   <si>
     <t>referencia</t>
   </si>
@@ -54,13 +54,7 @@
     <t>marca</t>
   </si>
   <si>
-    <t>negociador</t>
-  </si>
-  <si>
     <t>usuario</t>
-  </si>
-  <si>
-    <t>nombre</t>
   </si>
   <si>
     <t>MMIRANDA2</t>
@@ -72,13 +66,7 @@
     <t>PCARBONELL</t>
   </si>
   <si>
-    <t>Mileinis Miranda</t>
-  </si>
-  <si>
-    <t>Nicol Fernandez</t>
-  </si>
-  <si>
-    <t>Paola Carbonell</t>
+    <t>usuario_negociador</t>
   </si>
 </sst>
 </file>
@@ -194,13 +182,12 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FE82A2A1-8FD2-409E-B715-FAE4870AFD0F}" name="Tabla2" displayName="Tabla2" ref="A1:B4" totalsRowShown="0">
-  <autoFilter ref="A1:B4" xr:uid="{FE82A2A1-8FD2-409E-B715-FAE4870AFD0F}"/>
-  <tableColumns count="2">
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="2" xr:uid="{FE82A2A1-8FD2-409E-B715-FAE4870AFD0F}" name="Tabla2" displayName="Tabla2" ref="A1:A4" totalsRowShown="0">
+  <autoFilter ref="A1:A4" xr:uid="{FE82A2A1-8FD2-409E-B715-FAE4870AFD0F}"/>
+  <tableColumns count="1">
     <tableColumn id="1" xr3:uid="{906D9EC4-93F1-46F6-B1EF-540BF3388EBF}" name="usuario"/>
-    <tableColumn id="2" xr3:uid="{2DCD90C0-441C-4703-BDA3-36E1DC163D1E}" name="nombre"/>
   </tableColumns>
-  <tableStyleInfo name="TableStyleMedium3" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
+  <tableStyleInfo name="TableStyleLight8" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
 </file>
 
@@ -528,7 +515,7 @@
     <col min="2" max="2" width="15" style="2" customWidth="1"/>
     <col min="3" max="3" width="13" style="5" customWidth="1"/>
     <col min="4" max="5" width="10.69921875" style="2"/>
-    <col min="6" max="6" width="15.8984375" customWidth="1"/>
+    <col min="6" max="6" width="20.19921875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="19.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -548,7 +535,7 @@
         <v>4</v>
       </c>
       <c r="F1" s="6" t="s">
-        <v>5</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
@@ -1359,43 +1346,30 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8DEAF6A5-933D-4C2D-A63D-6B3D9DD19763}">
-  <dimension ref="A1:B4"/>
+  <dimension ref="A1:A4"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="16.3984375" customWidth="1"/>
-    <col min="2" max="2" width="30.5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>6</v>
       </c>
-      <c r="B1" t="s">
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A2" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>8</v>
-      </c>
-      <c r="B2" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4" t="s">
-        <v>13</v>
       </c>
     </row>
   </sheetData>
